--- a/api_testing/casos_api.xlsx
+++ b/api_testing/casos_api.xlsx
@@ -1,43 +1,219 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brenr\OneDrive\Desktop\Bren\ADA\QA TESTING\ProyectoFinal-Ruejas\api_testing\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C50C96-0BAE-4FCF-86D0-088CC68E2F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Método</t>
+  </si>
+  <si>
+    <t>Endpoint</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Resultado esperado</t>
+  </si>
+  <si>
+    <t>API-01</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>/products</t>
+  </si>
+  <si>
+    <t>Obtener lista de todos los productos</t>
+  </si>
+  <si>
+    <t>200 OK y Body con lista de productos &gt;= 1</t>
+  </si>
+  <si>
+    <t>API-02</t>
+  </si>
+  <si>
+    <t>/products/1</t>
+  </si>
+  <si>
+    <t>Obtener detalle de un producto específico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 OK y JSON con detalle del producto </t>
+  </si>
+  <si>
+    <t>API-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/products/categories </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obtener lista de categorías </t>
+  </si>
+  <si>
+    <t>200 OK y Body con el listado de categorías de los productos</t>
+  </si>
+  <si>
+    <t>API-04</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/products </t>
+  </si>
+  <si>
+    <t>Crear un producto nuevo</t>
+  </si>
+  <si>
+    <t>200/201 y producto nuevo creado</t>
+  </si>
+  <si>
+    <t>API-05</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/products/1 </t>
+  </si>
+  <si>
+    <t>Actualizar un producto</t>
+  </si>
+  <si>
+    <t>200 OK con datos actualizados</t>
+  </si>
+  <si>
+    <t>API-06</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>Eliminar producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 OK </t>
+  </si>
+  <si>
+    <t>API-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/products/9999 </t>
+  </si>
+  <si>
+    <t>Producto inexistente</t>
+  </si>
+  <si>
+    <t>404 Not Fount o Body vacío</t>
+  </si>
+  <si>
+    <t>API-08</t>
+  </si>
+  <si>
+    <t>Validar estructura JSON</t>
+  </si>
+  <si>
+    <t>Estructura con los datos esperados</t>
+  </si>
+  <si>
+    <t>API-09</t>
+  </si>
+  <si>
+    <t>/users</t>
+  </si>
+  <si>
+    <t>Obtener lista de usuarios</t>
+  </si>
+  <si>
+    <t>API-10</t>
+  </si>
+  <si>
+    <t>/cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obtener carritos </t>
+  </si>
+  <si>
+    <t>API-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/products/2 ; https://fakestoreapi.com/img/71-3HjGNDUL._AC_SY879._SX._UX._SY._UY_t.png </t>
+  </si>
+  <si>
+    <t>Visualizar imagen de un producto</t>
+  </si>
+  <si>
+    <t>200 OK e imagen del producto</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EA6B"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FFD4EA6B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,18 +221,116 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD4EA6B"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF81D41A"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -73,10 +347,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -114,116 +388,52 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -231,33 +441,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -270,13 +471,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -286,15 +481,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -302,7 +495,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -310,30 +502,236 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="62" customWidth="1"/>
+    <col min="4" max="4" width="52.21875" customWidth="1"/>
+    <col min="5" max="5" width="57.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api_testing/casos_api.xlsx
+++ b/api_testing/casos_api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brenr\OneDrive\Desktop\Bren\ADA\QA TESTING\ProyectoFinal-Ruejas\api_testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C50C96-0BAE-4FCF-86D0-088CC68E2F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFCCD0E-B819-4EBF-A316-ED104124AC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,9 +156,6 @@
     <t>API-10</t>
   </si>
   <si>
-    <t>/cars</t>
-  </si>
-  <si>
     <t xml:space="preserve">Obtener carritos </t>
   </si>
   <si>
@@ -172,6 +169,9 @@
   </si>
   <si>
     <t>200 OK e imagen del producto</t>
+  </si>
+  <si>
+    <t>/carts</t>
   </si>
 </sst>
 </file>
@@ -704,10 +704,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>31</v>
@@ -715,19 +715,19 @@
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/api_testing/casos_api.xlsx
+++ b/api_testing/casos_api.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brenr\OneDrive\Desktop\Bren\ADA\QA TESTING\ProyectoFinal-Ruejas\api_testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFCCD0E-B819-4EBF-A316-ED104124AC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AE7753-0860-4D0E-9EA9-393307D8478E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>ID</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>/carts</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
 </sst>
 </file>
@@ -240,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -257,6 +263,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="62" customWidth="1"/>
@@ -526,7 +533,7 @@
     <col min="5" max="5" width="57.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,8 +549,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -559,8 +569,11 @@
       <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F2" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -576,8 +589,11 @@
       <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F3" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -593,8 +609,11 @@
       <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F4" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -610,8 +629,11 @@
       <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F5" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -627,8 +649,11 @@
       <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F6" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -644,8 +669,11 @@
       <c r="E7" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F7" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -661,8 +689,11 @@
       <c r="E8" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F8" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
@@ -678,8 +709,11 @@
       <c r="E9" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F9" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
@@ -695,8 +729,11 @@
       <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F10" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
@@ -712,8 +749,11 @@
       <c r="E11" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F11" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -728,6 +768,9 @@
       </c>
       <c r="E12" s="4" t="s">
         <v>47</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
